--- a/Stock_OneClick/history/scan_result_20260603_095539.xlsx
+++ b/Stock_OneClick/history/scan_result_20260603_095539.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q245"/>
+  <dimension ref="A1:Q244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -670,24 +670,6 @@
       <c r="J3" t="n">
         <v>50.525</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-03; 相对D0=-0.27%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03</t>
@@ -739,24 +721,6 @@
       <c r="J4" t="n">
         <v>618.1</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-03; 相对D0=1.28%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-03</t>
@@ -808,24 +772,6 @@
       <c r="J5" t="n">
         <v>23.515</v>
       </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-03; 相对D0=4.46%; 本次触发=2026-06-03(预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-06-02, 2026-06-03</t>
@@ -877,24 +823,6 @@
       <c r="J6" t="n">
         <v>385.45</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-03; 相对D0=-0.78%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-03</t>
@@ -946,24 +874,12 @@
       <c r="J7" s="5" t="n">
         <v>119.14</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-03; 相对D0=3.08%; 本次触发=2026-06-03(正式买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-03</t>
@@ -1015,24 +931,6 @@
       <c r="J8" t="n">
         <v>69.38</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-03; 相对D0=-0.27%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1084,24 +982,12 @@
       <c r="J9" s="5" t="n">
         <v>40.88</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=40.13; 最新=2026-06-03; 相对D0=1.87%; 本次触发=2026-06-03(正式买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1153,24 +1039,12 @@
       <c r="J10" s="5" t="n">
         <v>32.065</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-03; 相对D0=23.99%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1222,24 +1096,6 @@
       <c r="J11" t="n">
         <v>282.8317</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=282.83; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1291,24 +1147,6 @@
       <c r="J12" t="n">
         <v>117.05</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=117.05; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1360,24 +1198,12 @@
       <c r="J13" s="5" t="n">
         <v>119.14</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=119.14; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入)</t>
@@ -1429,24 +1255,6 @@
       <c r="J14" t="n">
         <v>122.655</v>
       </c>
-      <c r="K14" t="n">
-        <v/>
-      </c>
-      <c r="L14" t="n">
-        <v/>
-      </c>
-      <c r="M14" t="n">
-        <v/>
-      </c>
-      <c r="N14" t="n">
-        <v/>
-      </c>
-      <c r="O14" t="n">
-        <v/>
-      </c>
-      <c r="P14" t="n">
-        <v/>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>D0=122.66; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1498,24 +1306,12 @@
       <c r="J15" s="5" t="n">
         <v>40.88</v>
       </c>
-      <c r="K15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O15" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P15" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
       <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>D0=40.88; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入)</t>
@@ -1567,24 +1363,6 @@
       <c r="J16" t="n">
         <v>50.525</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=50.52; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1636,24 +1414,6 @@
       <c r="J17" t="n">
         <v>509.35</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=509.35; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1705,24 +1465,6 @@
       <c r="J18" t="n">
         <v>618.1</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=618.10; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1774,24 +1516,6 @@
       <c r="J19" t="n">
         <v>80.56</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=80.56; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1843,24 +1567,6 @@
       <c r="J20" t="n">
         <v>23.515</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=23.52; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1912,24 +1618,6 @@
       <c r="J21" t="n">
         <v>69.38</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=69.38; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1981,24 +1669,12 @@
       <c r="J22" s="5" t="n">
         <v>32.065</v>
       </c>
-      <c r="K22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O22" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P22" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>D0=32.06; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2050,24 +1726,6 @@
       <c r="J23" t="n">
         <v>92.25</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=92.25; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -2119,24 +1777,6 @@
       <c r="J24" t="n">
         <v>385.45</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=385.45; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -2188,24 +1828,12 @@
       <c r="J25" s="5" t="n">
         <v>44.1514</v>
       </c>
-      <c r="K25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O25" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P25" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>D0=44.15; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2257,24 +1885,6 @@
       <c r="J26" t="n">
         <v>183.795</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-03; 相对D0=1.27%; 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -2326,24 +1936,12 @@
       <c r="J27" s="5" t="n">
         <v>185.705</v>
       </c>
-      <c r="K27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-03; 相对D0=-8.48%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2395,24 +1993,12 @@
       <c r="J28" s="5" t="n">
         <v>182.59</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-03; 相对D0=9.09%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -2464,24 +2050,12 @@
       <c r="J29" s="5" t="n">
         <v>266.115</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-03; 相对D0=-9.51%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -2533,24 +2107,12 @@
       <c r="J30" s="5" t="n">
         <v>56.29</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-03; 相对D0=20.98%</t>
@@ -2602,24 +2164,6 @@
       <c r="J31" t="n">
         <v>16.425</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-03; 相对D0=1.89%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2671,24 +2215,12 @@
       <c r="J32" s="5" t="n">
         <v>191.645</v>
       </c>
-      <c r="K32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O32" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P32" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-03; 相对D0=6.43%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2740,24 +2272,12 @@
       <c r="J33" s="5" t="n">
         <v>48.33</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-03; 相对D0=0.44%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -2809,24 +2329,12 @@
       <c r="J34" s="5" t="n">
         <v>140.73</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-03; 相对D0=4.03%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -2878,24 +2386,12 @@
       <c r="J35" s="5" t="n">
         <v>142.38</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-03; 相对D0=0.82%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -2947,24 +2443,12 @@
       <c r="J36" s="5" t="n">
         <v>419.22</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-03; 相对D0=7.12%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3016,24 +2500,12 @@
       <c r="J37" s="5" t="n">
         <v>963.29</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-03; 相对D0=-7.26%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3085,24 +2557,12 @@
       <c r="J38" s="5" t="n">
         <v>182.385</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-03; 相对D0=1.69%; 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
@@ -3154,24 +2614,12 @@
       <c r="J39" s="5" t="n">
         <v>371.16</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-03; 相对D0=13.81%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3223,24 +2671,12 @@
       <c r="J40" s="5" t="n">
         <v>25.86</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-03; 相对D0=-3.25%</t>
@@ -3292,24 +2728,12 @@
       <c r="J41" s="5" t="n">
         <v>133.575</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-03; 相对D0=-2.96%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -3361,24 +2785,6 @@
       <c r="J42" t="n">
         <v>258.4</v>
       </c>
-      <c r="K42" t="n">
-        <v/>
-      </c>
-      <c r="L42" t="n">
-        <v/>
-      </c>
-      <c r="M42" t="n">
-        <v/>
-      </c>
-      <c r="N42" t="n">
-        <v/>
-      </c>
-      <c r="O42" t="n">
-        <v/>
-      </c>
-      <c r="P42" t="n">
-        <v/>
-      </c>
       <c r="Q42" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-03; 相对D0=11.38%</t>
@@ -3430,24 +2836,6 @@
       <c r="J43" t="n">
         <v>144.01</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-03; 相对D0=10.35%</t>
@@ -3499,24 +2887,12 @@
       <c r="J44" s="5" t="n">
         <v>278.93</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-03; 相对D0=6.36%; 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -3568,24 +2944,12 @@
       <c r="J45" s="5" t="n">
         <v>60.225</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-03; 相对D0=2.41%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -3637,24 +3001,6 @@
       <c r="J46" t="n">
         <v>57.24</v>
       </c>
-      <c r="K46" t="n">
-        <v/>
-      </c>
-      <c r="L46" t="n">
-        <v/>
-      </c>
-      <c r="M46" t="n">
-        <v/>
-      </c>
-      <c r="N46" t="n">
-        <v/>
-      </c>
-      <c r="O46" t="n">
-        <v/>
-      </c>
-      <c r="P46" t="n">
-        <v/>
-      </c>
       <c r="Q46" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-03; 相对D0=4.19%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3706,24 +3052,6 @@
       <c r="J47" t="n">
         <v>87.7</v>
       </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-03; 相对D0=7.27%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3775,24 +3103,12 @@
       <c r="J48" s="5" t="n">
         <v>101.93</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-03; 相对D0=19.33%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3844,24 +3160,6 @@
       <c r="J49" t="n">
         <v>421.3</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-03; 相对D0=-1.11%</t>
@@ -3913,24 +3211,12 @@
       <c r="J50" s="5" t="n">
         <v>14.11</v>
       </c>
-      <c r="K50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O50" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P50" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K50" s="5" t="n"/>
+      <c r="L50" s="5" t="n"/>
+      <c r="M50" s="5" t="n"/>
+      <c r="N50" s="5" t="n"/>
+      <c r="O50" s="5" t="n"/>
+      <c r="P50" s="5" t="n"/>
       <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-03; 相对D0=8.37%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -3982,24 +3268,12 @@
       <c r="J51" s="5" t="n">
         <v>153.645</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-03; 相对D0=-1.68%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -4051,24 +3325,6 @@
       <c r="J52" t="n">
         <v>51.75</v>
       </c>
-      <c r="K52" t="n">
-        <v/>
-      </c>
-      <c r="L52" t="n">
-        <v/>
-      </c>
-      <c r="M52" t="n">
-        <v/>
-      </c>
-      <c r="N52" t="n">
-        <v/>
-      </c>
-      <c r="O52" t="n">
-        <v/>
-      </c>
-      <c r="P52" t="n">
-        <v/>
-      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-03; 相对D0=2.90%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4120,24 +3376,12 @@
       <c r="J53" s="5" t="n">
         <v>76.02500000000001</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-03; 相对D0=3.49%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4189,24 +3433,6 @@
       <c r="J54" t="n">
         <v>485.585</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-03; 相对D0=15.06%</t>
@@ -4258,24 +3484,6 @@
       <c r="J55" t="n">
         <v>90.87</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-03; 相对D0=5.06%</t>
@@ -4327,24 +3535,12 @@
       <c r="J56" s="5" t="n">
         <v>185.705</v>
       </c>
-      <c r="K56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O56" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P56" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K56" s="5" t="n"/>
+      <c r="L56" s="5" t="n"/>
+      <c r="M56" s="5" t="n"/>
+      <c r="N56" s="5" t="n"/>
+      <c r="O56" s="5" t="n"/>
+      <c r="P56" s="5" t="n"/>
       <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-03; 相对D0=-9.14%</t>
@@ -4396,24 +3592,12 @@
       <c r="J57" s="5" t="n">
         <v>182.59</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-03; 相对D0=4.50%</t>
@@ -4465,24 +3649,12 @@
       <c r="J58" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="K58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-03; 相对D0=5.39%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4534,24 +3706,6 @@
       <c r="J59" t="n">
         <v>111.9</v>
       </c>
-      <c r="K59" t="n">
-        <v/>
-      </c>
-      <c r="L59" t="n">
-        <v/>
-      </c>
-      <c r="M59" t="n">
-        <v/>
-      </c>
-      <c r="N59" t="n">
-        <v/>
-      </c>
-      <c r="O59" t="n">
-        <v/>
-      </c>
-      <c r="P59" t="n">
-        <v/>
-      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-03; 相对D0=5.68%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4603,24 +3757,12 @@
       <c r="J60" s="5" t="n">
         <v>48.33</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-03; 相对D0=-2.28%</t>
@@ -4672,24 +3814,12 @@
       <c r="J61" s="5" t="n">
         <v>419.22</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-03; 相对D0=3.99%</t>
@@ -4741,24 +3871,12 @@
       <c r="J62" s="5" t="n">
         <v>963.29</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-03; 相对D0=-10.01%</t>
@@ -4810,24 +3928,6 @@
       <c r="J63" t="n">
         <v>360.655</v>
       </c>
-      <c r="K63" t="n">
-        <v/>
-      </c>
-      <c r="L63" t="n">
-        <v/>
-      </c>
-      <c r="M63" t="n">
-        <v/>
-      </c>
-      <c r="N63" t="n">
-        <v/>
-      </c>
-      <c r="O63" t="n">
-        <v/>
-      </c>
-      <c r="P63" t="n">
-        <v/>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-03; 相对D0=-7.26%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4879,24 +3979,12 @@
       <c r="J64" s="5" t="n">
         <v>182.385</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-03; 相对D0=-0.53%</t>
@@ -4948,24 +4036,6 @@
       <c r="J65" t="n">
         <v>68.23</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
-      <c r="L65" t="n">
-        <v/>
-      </c>
-      <c r="M65" t="n">
-        <v/>
-      </c>
-      <c r="N65" t="n">
-        <v/>
-      </c>
-      <c r="O65" t="n">
-        <v/>
-      </c>
-      <c r="P65" t="n">
-        <v/>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-03; 相对D0=-2.01%</t>
@@ -5017,24 +4087,6 @@
       <c r="J66" t="n">
         <v>618.1</v>
       </c>
-      <c r="K66" t="n">
-        <v/>
-      </c>
-      <c r="L66" t="n">
-        <v/>
-      </c>
-      <c r="M66" t="n">
-        <v/>
-      </c>
-      <c r="N66" t="n">
-        <v/>
-      </c>
-      <c r="O66" t="n">
-        <v/>
-      </c>
-      <c r="P66" t="n">
-        <v/>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-03; 相对D0=0.94%</t>
@@ -5086,24 +4138,6 @@
       <c r="J67" t="n">
         <v>23.515</v>
       </c>
-      <c r="K67" t="n">
-        <v/>
-      </c>
-      <c r="L67" t="n">
-        <v/>
-      </c>
-      <c r="M67" t="n">
-        <v/>
-      </c>
-      <c r="N67" t="n">
-        <v/>
-      </c>
-      <c r="O67" t="n">
-        <v/>
-      </c>
-      <c r="P67" t="n">
-        <v/>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-03; 相对D0=3.96%</t>
@@ -5155,24 +4189,12 @@
       <c r="J68" s="5" t="n">
         <v>131.53</v>
       </c>
-      <c r="K68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O68" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P68" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K68" s="5" t="n"/>
+      <c r="L68" s="5" t="n"/>
+      <c r="M68" s="5" t="n"/>
+      <c r="N68" s="5" t="n"/>
+      <c r="O68" s="5" t="n"/>
+      <c r="P68" s="5" t="n"/>
       <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-03; 相对D0=-2.29%; 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -5224,24 +4246,12 @@
       <c r="J69" s="5" t="n">
         <v>64.92</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-03; 相对D0=-5.50%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5293,24 +4303,12 @@
       <c r="J70" s="5" t="n">
         <v>278.93</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-03; 相对D0=1.74%</t>
@@ -5362,24 +4360,6 @@
       <c r="J71" t="n">
         <v>57.24</v>
       </c>
-      <c r="K71" t="n">
-        <v/>
-      </c>
-      <c r="L71" t="n">
-        <v/>
-      </c>
-      <c r="M71" t="n">
-        <v/>
-      </c>
-      <c r="N71" t="n">
-        <v/>
-      </c>
-      <c r="O71" t="n">
-        <v/>
-      </c>
-      <c r="P71" t="n">
-        <v/>
-      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-03; 相对D0=1.65%</t>
@@ -5431,24 +4411,6 @@
       <c r="J72" t="n">
         <v>108.13</v>
       </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
-      <c r="L72" t="n">
-        <v/>
-      </c>
-      <c r="M72" t="n">
-        <v/>
-      </c>
-      <c r="N72" t="n">
-        <v/>
-      </c>
-      <c r="O72" t="n">
-        <v/>
-      </c>
-      <c r="P72" t="n">
-        <v/>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-03; 相对D0=1.11%</t>
@@ -5500,24 +4462,12 @@
       <c r="J73" s="5" t="n">
         <v>12.1164</v>
       </c>
-      <c r="K73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O73" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P73" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K73" s="5" t="n"/>
+      <c r="L73" s="5" t="n"/>
+      <c r="M73" s="5" t="n"/>
+      <c r="N73" s="5" t="n"/>
+      <c r="O73" s="5" t="n"/>
+      <c r="P73" s="5" t="n"/>
       <c r="Q73" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-03; 相对D0=-0.85%</t>
@@ -5569,24 +4519,6 @@
       <c r="J74" t="n">
         <v>16.605</v>
       </c>
-      <c r="K74" t="n">
-        <v/>
-      </c>
-      <c r="L74" t="n">
-        <v/>
-      </c>
-      <c r="M74" t="n">
-        <v/>
-      </c>
-      <c r="N74" t="n">
-        <v/>
-      </c>
-      <c r="O74" t="n">
-        <v/>
-      </c>
-      <c r="P74" t="n">
-        <v/>
-      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-03; 相对D0=3.91%</t>
@@ -5638,24 +4570,6 @@
       <c r="J75" t="n">
         <v>87.7</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-03; 相对D0=3.62%</t>
@@ -5707,24 +4621,12 @@
       <c r="J76" s="5" t="n">
         <v>14.11</v>
       </c>
-      <c r="K76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O76" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P76" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K76" s="5" t="n"/>
+      <c r="L76" s="5" t="n"/>
+      <c r="M76" s="5" t="n"/>
+      <c r="N76" s="5" t="n"/>
+      <c r="O76" s="5" t="n"/>
+      <c r="P76" s="5" t="n"/>
       <c r="Q76" s="5" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-03; 相对D0=4.44%</t>
@@ -5776,24 +4678,12 @@
       <c r="J77" s="5" t="n">
         <v>17.93</v>
       </c>
-      <c r="K77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
       <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-03; 相对D0=-2.55%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5845,24 +4735,6 @@
       <c r="J78" t="n">
         <v>333.17</v>
       </c>
-      <c r="K78" t="n">
-        <v/>
-      </c>
-      <c r="L78" t="n">
-        <v/>
-      </c>
-      <c r="M78" t="n">
-        <v/>
-      </c>
-      <c r="N78" t="n">
-        <v/>
-      </c>
-      <c r="O78" t="n">
-        <v/>
-      </c>
-      <c r="P78" t="n">
-        <v/>
-      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-03; 相对D0=2.86%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5914,24 +4786,6 @@
       <c r="J79" t="n">
         <v>51.75</v>
       </c>
-      <c r="K79" t="n">
-        <v/>
-      </c>
-      <c r="L79" t="n">
-        <v/>
-      </c>
-      <c r="M79" t="n">
-        <v/>
-      </c>
-      <c r="N79" t="n">
-        <v/>
-      </c>
-      <c r="O79" t="n">
-        <v/>
-      </c>
-      <c r="P79" t="n">
-        <v/>
-      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-03; 相对D0=1.49%</t>
@@ -5983,24 +4837,6 @@
       <c r="J80" t="n">
         <v>183.795</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-03; 相对D0=2.20%</t>
@@ -6052,24 +4888,6 @@
       <c r="J81" t="n">
         <v>248.65</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-03; 相对D0=-8.53%</t>
@@ -6090,7 +4908,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6117,24 +4934,6 @@
       <c r="J82" t="n">
         <v>91.08</v>
       </c>
-      <c r="K82" t="n">
-        <v/>
-      </c>
-      <c r="L82" t="n">
-        <v/>
-      </c>
-      <c r="M82" t="n">
-        <v/>
-      </c>
-      <c r="N82" t="n">
-        <v/>
-      </c>
-      <c r="O82" t="n">
-        <v/>
-      </c>
-      <c r="P82" t="n">
-        <v/>
-      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-03; 相对D0=0.23%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6186,24 +4985,6 @@
       <c r="J83" t="n">
         <v>16.425</v>
       </c>
-      <c r="K83" t="n">
-        <v/>
-      </c>
-      <c r="L83" t="n">
-        <v/>
-      </c>
-      <c r="M83" t="n">
-        <v/>
-      </c>
-      <c r="N83" t="n">
-        <v/>
-      </c>
-      <c r="O83" t="n">
-        <v/>
-      </c>
-      <c r="P83" t="n">
-        <v/>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-03; 相对D0=-0.21%</t>
@@ -6255,24 +5036,6 @@
       <c r="J84" t="n">
         <v>26.52</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-03; 相对D0=5.24%</t>
@@ -6324,24 +5087,6 @@
       <c r="J85" t="n">
         <v>83.22</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-03; 相对D0=9.17%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6393,24 +5138,6 @@
       <c r="J86" t="n">
         <v>50.525</v>
       </c>
-      <c r="K86" t="n">
-        <v/>
-      </c>
-      <c r="L86" t="n">
-        <v/>
-      </c>
-      <c r="M86" t="n">
-        <v/>
-      </c>
-      <c r="N86" t="n">
-        <v/>
-      </c>
-      <c r="O86" t="n">
-        <v/>
-      </c>
-      <c r="P86" t="n">
-        <v/>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-03; 相对D0=0.17%</t>
@@ -6462,24 +5189,12 @@
       <c r="J87" s="5" t="n">
         <v>119.54</v>
       </c>
-      <c r="K87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O87" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P87" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K87" s="5" t="n"/>
+      <c r="L87" s="5" t="n"/>
+      <c r="M87" s="5" t="n"/>
+      <c r="N87" s="5" t="n"/>
+      <c r="O87" s="5" t="n"/>
+      <c r="P87" s="5" t="n"/>
       <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-03; 相对D0=17.06%</t>
@@ -6531,24 +5246,12 @@
       <c r="J88" s="5" t="n">
         <v>278.93</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-03; 相对D0=4.51%</t>
@@ -6600,24 +5303,6 @@
       <c r="J89" t="n">
         <v>228.73</v>
       </c>
-      <c r="K89" t="n">
-        <v/>
-      </c>
-      <c r="L89" t="n">
-        <v/>
-      </c>
-      <c r="M89" t="n">
-        <v/>
-      </c>
-      <c r="N89" t="n">
-        <v/>
-      </c>
-      <c r="O89" t="n">
-        <v/>
-      </c>
-      <c r="P89" t="n">
-        <v/>
-      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-03; 相对D0=19.78%</t>
@@ -6669,24 +5354,12 @@
       <c r="J90" s="5" t="n">
         <v>101.93</v>
       </c>
-      <c r="K90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O90" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P90" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K90" s="5" t="n"/>
+      <c r="L90" s="5" t="n"/>
+      <c r="M90" s="5" t="n"/>
+      <c r="N90" s="5" t="n"/>
+      <c r="O90" s="5" t="n"/>
+      <c r="P90" s="5" t="n"/>
       <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-03; 相对D0=14.44%</t>
@@ -6738,24 +5411,6 @@
       <c r="J91" t="n">
         <v>385.45</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-03; 相对D0=0.37%</t>
@@ -6807,24 +5462,6 @@
       <c r="J92" t="n">
         <v>286.4675</v>
       </c>
-      <c r="K92" t="n">
-        <v/>
-      </c>
-      <c r="L92" t="n">
-        <v/>
-      </c>
-      <c r="M92" t="n">
-        <v/>
-      </c>
-      <c r="N92" t="n">
-        <v/>
-      </c>
-      <c r="O92" t="n">
-        <v/>
-      </c>
-      <c r="P92" t="n">
-        <v/>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-03; 相对D0=-1.22%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -6845,7 +5482,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6872,24 +5508,6 @@
       <c r="J93" t="n">
         <v>91.08</v>
       </c>
-      <c r="K93" t="n">
-        <v/>
-      </c>
-      <c r="L93" t="n">
-        <v/>
-      </c>
-      <c r="M93" t="n">
-        <v/>
-      </c>
-      <c r="N93" t="n">
-        <v/>
-      </c>
-      <c r="O93" t="n">
-        <v/>
-      </c>
-      <c r="P93" t="n">
-        <v/>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-03; 相对D0=-0.01%</t>
@@ -6941,24 +5559,12 @@
       <c r="J94" s="5" t="n">
         <v>114</v>
       </c>
-      <c r="K94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O94" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P94" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K94" s="5" t="n"/>
+      <c r="L94" s="5" t="n"/>
+      <c r="M94" s="5" t="n"/>
+      <c r="N94" s="5" t="n"/>
+      <c r="O94" s="5" t="n"/>
+      <c r="P94" s="5" t="n"/>
       <c r="Q94" s="5" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-03; 相对D0=3.05%</t>
@@ -7010,24 +5616,6 @@
       <c r="J95" t="n">
         <v>91.79000000000001</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-03; 相对D0=9.69%</t>
@@ -7079,24 +5667,12 @@
       <c r="J96" s="5" t="n">
         <v>191.645</v>
       </c>
-      <c r="K96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O96" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P96" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K96" s="5" t="n"/>
+      <c r="L96" s="5" t="n"/>
+      <c r="M96" s="5" t="n"/>
+      <c r="N96" s="5" t="n"/>
+      <c r="O96" s="5" t="n"/>
+      <c r="P96" s="5" t="n"/>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-03; 相对D0=8.78%</t>
@@ -7148,24 +5724,6 @@
       <c r="J97" t="n">
         <v>748.03</v>
       </c>
-      <c r="K97" t="n">
-        <v/>
-      </c>
-      <c r="L97" t="n">
-        <v/>
-      </c>
-      <c r="M97" t="n">
-        <v/>
-      </c>
-      <c r="N97" t="n">
-        <v/>
-      </c>
-      <c r="O97" t="n">
-        <v/>
-      </c>
-      <c r="P97" t="n">
-        <v/>
-      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-03; 相对D0=11.48%</t>
@@ -7217,24 +5775,6 @@
       <c r="J98" t="n">
         <v>111.9</v>
       </c>
-      <c r="K98" t="n">
-        <v/>
-      </c>
-      <c r="L98" t="n">
-        <v/>
-      </c>
-      <c r="M98" t="n">
-        <v/>
-      </c>
-      <c r="N98" t="n">
-        <v/>
-      </c>
-      <c r="O98" t="n">
-        <v/>
-      </c>
-      <c r="P98" t="n">
-        <v/>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-03; 相对D0=4.72%</t>
@@ -7286,24 +5826,6 @@
       <c r="J99" t="n">
         <v>66.345</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-03; 相对D0=-1.54%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -7324,7 +5846,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7351,24 +5872,6 @@
       <c r="J100" t="n">
         <v>1096.14</v>
       </c>
-      <c r="K100" t="n">
-        <v/>
-      </c>
-      <c r="L100" t="n">
-        <v/>
-      </c>
-      <c r="M100" t="n">
-        <v/>
-      </c>
-      <c r="N100" t="n">
-        <v/>
-      </c>
-      <c r="O100" t="n">
-        <v/>
-      </c>
-      <c r="P100" t="n">
-        <v/>
-      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-03; 相对D0=2.50%</t>
@@ -7420,24 +5923,6 @@
       <c r="J101" t="n">
         <v>146.455</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-03; 相对D0=12.92%</t>
@@ -7489,24 +5974,6 @@
       <c r="J102" t="n">
         <v>360.655</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-03; 相对D0=-7.56%</t>
@@ -7558,24 +6025,6 @@
       <c r="J103" t="n">
         <v>83.22</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-03; 相对D0=-1.91%</t>
@@ -7627,24 +6076,12 @@
       <c r="J104" s="5" t="n">
         <v>100.035</v>
       </c>
-      <c r="K104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O104" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P104" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K104" s="5" t="n"/>
+      <c r="L104" s="5" t="n"/>
+      <c r="M104" s="5" t="n"/>
+      <c r="N104" s="5" t="n"/>
+      <c r="O104" s="5" t="n"/>
+      <c r="P104" s="5" t="n"/>
       <c r="Q104" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-03; 相对D0=4.55%</t>
@@ -7696,24 +6133,12 @@
       <c r="J105" s="5" t="n">
         <v>182.385</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-03; 相对D0=-1.66%</t>
@@ -7765,24 +6190,12 @@
       <c r="J106" s="5" t="n">
         <v>371.16</v>
       </c>
-      <c r="K106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P106" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
       <c r="Q106" s="5" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-03; 相对D0=13.96%</t>
@@ -7834,24 +6247,6 @@
       <c r="J107" t="n">
         <v>424.65</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-03; 相对D0=-0.55%</t>
@@ -7903,24 +6298,6 @@
       <c r="J108" t="n">
         <v>249.99</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-03; 相对D0=10.45%</t>
@@ -7972,24 +6349,12 @@
       <c r="J109" s="5" t="n">
         <v>131.53</v>
       </c>
-      <c r="K109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O109" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P109" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K109" s="5" t="n"/>
+      <c r="L109" s="5" t="n"/>
+      <c r="M109" s="5" t="n"/>
+      <c r="N109" s="5" t="n"/>
+      <c r="O109" s="5" t="n"/>
+      <c r="P109" s="5" t="n"/>
       <c r="Q109" s="5" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-03; 相对D0=-1.34%</t>
@@ -8041,24 +6406,6 @@
       <c r="J110" t="n">
         <v>124.61</v>
       </c>
-      <c r="K110" t="n">
-        <v/>
-      </c>
-      <c r="L110" t="n">
-        <v/>
-      </c>
-      <c r="M110" t="n">
-        <v/>
-      </c>
-      <c r="N110" t="n">
-        <v/>
-      </c>
-      <c r="O110" t="n">
-        <v/>
-      </c>
-      <c r="P110" t="n">
-        <v/>
-      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-03; 相对D0=31.56%</t>
@@ -8110,24 +6457,6 @@
       <c r="J111" t="n">
         <v>280.04</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-03; 相对D0=8.64%</t>
@@ -8179,24 +6508,12 @@
       <c r="J112" s="5" t="n">
         <v>142.715</v>
       </c>
-      <c r="K112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P112" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K112" s="5" t="n"/>
+      <c r="L112" s="5" t="n"/>
+      <c r="M112" s="5" t="n"/>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
       <c r="Q112" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-03; 相对D0=-0.44%</t>
@@ -8248,24 +6565,12 @@
       <c r="J113" s="5" t="n">
         <v>256.38</v>
       </c>
-      <c r="K113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P113" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="5" t="n"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
       <c r="Q113" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-03; 相对D0=-1.09%</t>
@@ -8317,24 +6622,12 @@
       <c r="J114" s="5" t="n">
         <v>182.59</v>
       </c>
-      <c r="K114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="n"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
       <c r="Q114" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-03; 相对D0=6.37%</t>
@@ -8386,24 +6679,12 @@
       <c r="J115" s="5" t="n">
         <v>266.115</v>
       </c>
-      <c r="K115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P115" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="5" t="n"/>
+      <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="5" t="n"/>
       <c r="Q115" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-03; 相对D0=-7.52%</t>
@@ -8455,24 +6736,6 @@
       <c r="J116" t="n">
         <v>164.8299</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-03; 相对D0=-12.80%</t>
@@ -8524,24 +6787,12 @@
       <c r="J117" s="5" t="n">
         <v>191.645</v>
       </c>
-      <c r="K117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P117" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K117" s="5" t="n"/>
+      <c r="L117" s="5" t="n"/>
+      <c r="M117" s="5" t="n"/>
+      <c r="N117" s="5" t="n"/>
+      <c r="O117" s="5" t="n"/>
+      <c r="P117" s="5" t="n"/>
       <c r="Q117" s="5" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-03; 相对D0=0.29%</t>
@@ -8593,24 +6844,6 @@
       <c r="J118" t="n">
         <v>111.9</v>
       </c>
-      <c r="K118" t="n">
-        <v/>
-      </c>
-      <c r="L118" t="n">
-        <v/>
-      </c>
-      <c r="M118" t="n">
-        <v/>
-      </c>
-      <c r="N118" t="n">
-        <v/>
-      </c>
-      <c r="O118" t="n">
-        <v/>
-      </c>
-      <c r="P118" t="n">
-        <v/>
-      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-03; 相对D0=2.16%</t>
@@ -8662,24 +6895,12 @@
       <c r="J119" s="5" t="n">
         <v>48.33</v>
       </c>
-      <c r="K119" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L119" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M119" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N119" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O119" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P119" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K119" s="5" t="n"/>
+      <c r="L119" s="5" t="n"/>
+      <c r="M119" s="5" t="n"/>
+      <c r="N119" s="5" t="n"/>
+      <c r="O119" s="5" t="n"/>
+      <c r="P119" s="5" t="n"/>
       <c r="Q119" s="5" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-03; 相对D0=-0.19%</t>
@@ -8731,24 +6952,6 @@
       <c r="J120" t="n">
         <v>2098.28</v>
       </c>
-      <c r="K120" t="n">
-        <v/>
-      </c>
-      <c r="L120" t="n">
-        <v/>
-      </c>
-      <c r="M120" t="n">
-        <v/>
-      </c>
-      <c r="N120" t="n">
-        <v/>
-      </c>
-      <c r="O120" t="n">
-        <v/>
-      </c>
-      <c r="P120" t="n">
-        <v/>
-      </c>
       <c r="Q120" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-03; 相对D0=9.19%</t>
@@ -8800,24 +7003,12 @@
       <c r="J121" s="5" t="n">
         <v>371.16</v>
       </c>
-      <c r="K121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P121" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="5" t="n"/>
+      <c r="M121" s="5" t="n"/>
+      <c r="N121" s="5" t="n"/>
+      <c r="O121" s="5" t="n"/>
+      <c r="P121" s="5" t="n"/>
       <c r="Q121" s="5" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-03; 相对D0=10.61%</t>
@@ -8869,24 +7060,6 @@
       <c r="J122" t="n">
         <v>215.68</v>
       </c>
-      <c r="K122" t="n">
-        <v/>
-      </c>
-      <c r="L122" t="n">
-        <v/>
-      </c>
-      <c r="M122" t="n">
-        <v/>
-      </c>
-      <c r="N122" t="n">
-        <v/>
-      </c>
-      <c r="O122" t="n">
-        <v/>
-      </c>
-      <c r="P122" t="n">
-        <v/>
-      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-03; 相对D0=2.15%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -8938,24 +7111,12 @@
       <c r="J123" s="5" t="n">
         <v>405.2825</v>
       </c>
-      <c r="K123" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L123" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N123" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O123" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P123" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K123" s="5" t="n"/>
+      <c r="L123" s="5" t="n"/>
+      <c r="M123" s="5" t="n"/>
+      <c r="N123" s="5" t="n"/>
+      <c r="O123" s="5" t="n"/>
+      <c r="P123" s="5" t="n"/>
       <c r="Q123" s="5" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-03; 相对D0=8.27%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9007,24 +7168,12 @@
       <c r="J124" s="5" t="n">
         <v>14.11</v>
       </c>
-      <c r="K124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-03; 相对D0=2.47%</t>
@@ -9076,24 +7225,6 @@
       <c r="J125" t="n">
         <v>50.895</v>
       </c>
-      <c r="K125" t="n">
-        <v/>
-      </c>
-      <c r="L125" t="n">
-        <v/>
-      </c>
-      <c r="M125" t="n">
-        <v/>
-      </c>
-      <c r="N125" t="n">
-        <v/>
-      </c>
-      <c r="O125" t="n">
-        <v/>
-      </c>
-      <c r="P125" t="n">
-        <v/>
-      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-03; 相对D0=-1.33%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9145,24 +7276,6 @@
       <c r="J126" t="n">
         <v>183.795</v>
       </c>
-      <c r="K126" t="n">
-        <v/>
-      </c>
-      <c r="L126" t="n">
-        <v/>
-      </c>
-      <c r="M126" t="n">
-        <v/>
-      </c>
-      <c r="N126" t="n">
-        <v/>
-      </c>
-      <c r="O126" t="n">
-        <v/>
-      </c>
-      <c r="P126" t="n">
-        <v/>
-      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-03; 相对D0=-1.01%</t>
@@ -9214,24 +7327,12 @@
       <c r="J127" s="5" t="n">
         <v>14.72</v>
       </c>
-      <c r="K127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O127" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P127" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K127" s="5" t="n"/>
+      <c r="L127" s="5" t="n"/>
+      <c r="M127" s="5" t="n"/>
+      <c r="N127" s="5" t="n"/>
+      <c r="O127" s="5" t="n"/>
+      <c r="P127" s="5" t="n"/>
       <c r="Q127" s="5" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-03; 相对D0=0.14%</t>
@@ -9283,24 +7384,12 @@
       <c r="J128" s="5" t="n">
         <v>76.02500000000001</v>
       </c>
-      <c r="K128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-03; 相对D0=4.50%</t>
@@ -9352,24 +7441,6 @@
       <c r="J129" t="n">
         <v>315.07</v>
       </c>
-      <c r="K129" t="n">
-        <v/>
-      </c>
-      <c r="L129" t="n">
-        <v/>
-      </c>
-      <c r="M129" t="n">
-        <v/>
-      </c>
-      <c r="N129" t="n">
-        <v/>
-      </c>
-      <c r="O129" t="n">
-        <v/>
-      </c>
-      <c r="P129" t="n">
-        <v/>
-      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-03; 相对D0=-1.67%</t>
@@ -9421,24 +7492,12 @@
       <c r="J130" s="5" t="n">
         <v>191.01</v>
       </c>
-      <c r="K130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K130" s="5" t="n"/>
+      <c r="L130" s="5" t="n"/>
+      <c r="M130" s="5" t="n"/>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
       <c r="Q130" s="5" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-03; 相对D0=2.79%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9490,24 +7549,12 @@
       <c r="J131" s="5" t="n">
         <v>142.38</v>
       </c>
-      <c r="K131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="5" t="n"/>
+      <c r="M131" s="5" t="n"/>
+      <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="5" t="n"/>
       <c r="Q131" s="5" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-03; 相对D0=4.22%</t>
@@ -9559,24 +7606,6 @@
       <c r="J132" t="n">
         <v>8.435</v>
       </c>
-      <c r="K132" t="n">
-        <v/>
-      </c>
-      <c r="L132" t="n">
-        <v/>
-      </c>
-      <c r="M132" t="n">
-        <v/>
-      </c>
-      <c r="N132" t="n">
-        <v/>
-      </c>
-      <c r="O132" t="n">
-        <v/>
-      </c>
-      <c r="P132" t="n">
-        <v/>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-03; 相对D0=-5.96%</t>
@@ -9628,24 +7657,6 @@
       <c r="J133" t="n">
         <v>25.205</v>
       </c>
-      <c r="K133" t="n">
-        <v/>
-      </c>
-      <c r="L133" t="n">
-        <v/>
-      </c>
-      <c r="M133" t="n">
-        <v/>
-      </c>
-      <c r="N133" t="n">
-        <v/>
-      </c>
-      <c r="O133" t="n">
-        <v/>
-      </c>
-      <c r="P133" t="n">
-        <v/>
-      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-03; 相对D0=-7.16%</t>
@@ -9697,24 +7708,6 @@
       <c r="J134" t="n">
         <v>50.525</v>
       </c>
-      <c r="K134" t="n">
-        <v/>
-      </c>
-      <c r="L134" t="n">
-        <v/>
-      </c>
-      <c r="M134" t="n">
-        <v/>
-      </c>
-      <c r="N134" t="n">
-        <v/>
-      </c>
-      <c r="O134" t="n">
-        <v/>
-      </c>
-      <c r="P134" t="n">
-        <v/>
-      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-03; 相对D0=-0.05%</t>
@@ -9766,24 +7759,12 @@
       <c r="J135" s="5" t="n">
         <v>182.385</v>
       </c>
-      <c r="K135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K135" s="5" t="n"/>
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="5" t="n"/>
+      <c r="N135" s="5" t="n"/>
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="5" t="n"/>
       <c r="Q135" s="5" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-03; 相对D0=-3.50%</t>
@@ -9835,24 +7816,6 @@
       <c r="J136" t="n">
         <v>943.62</v>
       </c>
-      <c r="K136" t="n">
-        <v/>
-      </c>
-      <c r="L136" t="n">
-        <v/>
-      </c>
-      <c r="M136" t="n">
-        <v/>
-      </c>
-      <c r="N136" t="n">
-        <v/>
-      </c>
-      <c r="O136" t="n">
-        <v/>
-      </c>
-      <c r="P136" t="n">
-        <v/>
-      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-03; 相对D0=4.27%</t>
@@ -9904,24 +7867,6 @@
       <c r="J137" t="n">
         <v>12.31</v>
       </c>
-      <c r="K137" t="n">
-        <v/>
-      </c>
-      <c r="L137" t="n">
-        <v/>
-      </c>
-      <c r="M137" t="n">
-        <v/>
-      </c>
-      <c r="N137" t="n">
-        <v/>
-      </c>
-      <c r="O137" t="n">
-        <v/>
-      </c>
-      <c r="P137" t="n">
-        <v/>
-      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-03; 相对D0=11.71%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9973,24 +7918,6 @@
       <c r="J138" t="n">
         <v>215.68</v>
       </c>
-      <c r="K138" t="n">
-        <v/>
-      </c>
-      <c r="L138" t="n">
-        <v/>
-      </c>
-      <c r="M138" t="n">
-        <v/>
-      </c>
-      <c r="N138" t="n">
-        <v/>
-      </c>
-      <c r="O138" t="n">
-        <v/>
-      </c>
-      <c r="P138" t="n">
-        <v/>
-      </c>
       <c r="Q138" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-03; 相对D0=-3.87%</t>
@@ -10042,24 +7969,12 @@
       <c r="J139" s="5" t="n">
         <v>64.92</v>
       </c>
-      <c r="K139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O139" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P139" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K139" s="5" t="n"/>
+      <c r="L139" s="5" t="n"/>
+      <c r="M139" s="5" t="n"/>
+      <c r="N139" s="5" t="n"/>
+      <c r="O139" s="5" t="n"/>
+      <c r="P139" s="5" t="n"/>
       <c r="Q139" s="5" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-03; 相对D0=-2.95%</t>
@@ -10111,24 +8026,12 @@
       <c r="J140" s="5" t="n">
         <v>60.225</v>
       </c>
-      <c r="K140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="5" t="n"/>
+      <c r="L140" s="5" t="n"/>
+      <c r="M140" s="5" t="n"/>
+      <c r="N140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
+      <c r="P140" s="5" t="n"/>
       <c r="Q140" s="5" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-03; 相对D0=2.21%</t>
@@ -10180,24 +8083,6 @@
       <c r="J141" t="n">
         <v>14.42</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-03; 相对D0=3.82%</t>
@@ -10249,24 +8134,6 @@
       <c r="J142" t="n">
         <v>14.745</v>
       </c>
-      <c r="K142" t="n">
-        <v/>
-      </c>
-      <c r="L142" t="n">
-        <v/>
-      </c>
-      <c r="M142" t="n">
-        <v/>
-      </c>
-      <c r="N142" t="n">
-        <v/>
-      </c>
-      <c r="O142" t="n">
-        <v/>
-      </c>
-      <c r="P142" t="n">
-        <v/>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-03; 相对D0=-5.36%</t>
@@ -10318,24 +8185,12 @@
       <c r="J143" s="5" t="n">
         <v>17.93</v>
       </c>
-      <c r="K143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O143" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P143" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K143" s="5" t="n"/>
+      <c r="L143" s="5" t="n"/>
+      <c r="M143" s="5" t="n"/>
+      <c r="N143" s="5" t="n"/>
+      <c r="O143" s="5" t="n"/>
+      <c r="P143" s="5" t="n"/>
       <c r="Q143" s="5" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-03; 相对D0=1.76%</t>
@@ -10387,24 +8242,6 @@
       <c r="J144" t="n">
         <v>333.17</v>
       </c>
-      <c r="K144" t="n">
-        <v/>
-      </c>
-      <c r="L144" t="n">
-        <v/>
-      </c>
-      <c r="M144" t="n">
-        <v/>
-      </c>
-      <c r="N144" t="n">
-        <v/>
-      </c>
-      <c r="O144" t="n">
-        <v/>
-      </c>
-      <c r="P144" t="n">
-        <v/>
-      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-03; 相对D0=3.02%</t>
@@ -10456,24 +8293,6 @@
       <c r="J145" t="n">
         <v>133.825</v>
       </c>
-      <c r="K145" t="n">
-        <v/>
-      </c>
-      <c r="L145" t="n">
-        <v/>
-      </c>
-      <c r="M145" t="n">
-        <v/>
-      </c>
-      <c r="N145" t="n">
-        <v/>
-      </c>
-      <c r="O145" t="n">
-        <v/>
-      </c>
-      <c r="P145" t="n">
-        <v/>
-      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-03; 相对D0=-14.05%</t>
@@ -10525,24 +8344,6 @@
       <c r="J146" t="n">
         <v>310.09</v>
       </c>
-      <c r="K146" t="n">
-        <v/>
-      </c>
-      <c r="L146" t="n">
-        <v/>
-      </c>
-      <c r="M146" t="n">
-        <v/>
-      </c>
-      <c r="N146" t="n">
-        <v/>
-      </c>
-      <c r="O146" t="n">
-        <v/>
-      </c>
-      <c r="P146" t="n">
-        <v/>
-      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>D0=315.20; 最新=2026-06-03; 相对D0=-1.62%</t>
@@ -10594,24 +8395,12 @@
       <c r="J147" s="5" t="n">
         <v>116.63</v>
       </c>
-      <c r="K147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O147" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P147" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K147" s="5" t="n"/>
+      <c r="L147" s="5" t="n"/>
+      <c r="M147" s="5" t="n"/>
+      <c r="N147" s="5" t="n"/>
+      <c r="O147" s="5" t="n"/>
+      <c r="P147" s="5" t="n"/>
       <c r="Q147" s="5" t="inlineStr">
         <is>
           <t>D0=113.00; 最新=2026-06-03; 相对D0=3.21%</t>
@@ -10663,24 +8452,6 @@
       <c r="J148" t="n">
         <v>107.065</v>
       </c>
-      <c r="K148" t="n">
-        <v/>
-      </c>
-      <c r="L148" t="n">
-        <v/>
-      </c>
-      <c r="M148" t="n">
-        <v/>
-      </c>
-      <c r="N148" t="n">
-        <v/>
-      </c>
-      <c r="O148" t="n">
-        <v/>
-      </c>
-      <c r="P148" t="n">
-        <v/>
-      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>D0=118.17; 最新=2026-06-03; 相对D0=-9.40%</t>
@@ -10732,24 +8503,6 @@
       <c r="J149" t="n">
         <v>286.4675</v>
       </c>
-      <c r="K149" t="n">
-        <v/>
-      </c>
-      <c r="L149" t="n">
-        <v/>
-      </c>
-      <c r="M149" t="n">
-        <v/>
-      </c>
-      <c r="N149" t="n">
-        <v/>
-      </c>
-      <c r="O149" t="n">
-        <v/>
-      </c>
-      <c r="P149" t="n">
-        <v/>
-      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>D0=302.85; 最新=2026-06-03; 相对D0=-5.41%</t>
@@ -10801,24 +8554,12 @@
       <c r="J150" s="5" t="n">
         <v>182.59</v>
       </c>
-      <c r="K150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O150" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P150" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="5" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="5" t="n"/>
       <c r="Q150" s="5" t="inlineStr">
         <is>
           <t>D0=187.52; 最新=2026-06-03; 相对D0=-2.63%</t>
@@ -10870,24 +8611,6 @@
       <c r="J151" t="n">
         <v>415.545</v>
       </c>
-      <c r="K151" t="n">
-        <v/>
-      </c>
-      <c r="L151" t="n">
-        <v/>
-      </c>
-      <c r="M151" t="n">
-        <v/>
-      </c>
-      <c r="N151" t="n">
-        <v/>
-      </c>
-      <c r="O151" t="n">
-        <v/>
-      </c>
-      <c r="P151" t="n">
-        <v/>
-      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>D0=426.89; 最新=2026-06-03; 相对D0=-2.66%</t>
@@ -10939,24 +8662,12 @@
       <c r="J152" s="5" t="n">
         <v>119.14</v>
       </c>
-      <c r="K152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="5" t="n"/>
+      <c r="L152" s="5" t="n"/>
+      <c r="M152" s="5" t="n"/>
+      <c r="N152" s="5" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="5" t="n"/>
       <c r="Q152" s="5" t="inlineStr">
         <is>
           <t>D0=116.87; 最新=2026-06-03; 相对D0=1.94%</t>
@@ -11008,24 +8719,6 @@
       <c r="J153" t="n">
         <v>208.775</v>
       </c>
-      <c r="K153" t="n">
-        <v/>
-      </c>
-      <c r="L153" t="n">
-        <v/>
-      </c>
-      <c r="M153" t="n">
-        <v/>
-      </c>
-      <c r="N153" t="n">
-        <v/>
-      </c>
-      <c r="O153" t="n">
-        <v/>
-      </c>
-      <c r="P153" t="n">
-        <v/>
-      </c>
       <c r="Q153" t="inlineStr">
         <is>
           <t>D0=229.00; 最新=2026-06-03; 相对D0=-8.83%</t>
@@ -11077,24 +8770,12 @@
       <c r="J154" s="5" t="n">
         <v>191.01</v>
       </c>
-      <c r="K154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P154" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K154" s="5" t="n"/>
+      <c r="L154" s="5" t="n"/>
+      <c r="M154" s="5" t="n"/>
+      <c r="N154" s="5" t="n"/>
+      <c r="O154" s="5" t="n"/>
+      <c r="P154" s="5" t="n"/>
       <c r="Q154" s="5" t="inlineStr">
         <is>
           <t>D0=187.55; 最新=2026-06-03; 相对D0=1.84%</t>
@@ -11146,24 +8827,6 @@
       <c r="J155" t="n">
         <v>66.345</v>
       </c>
-      <c r="K155" t="n">
-        <v/>
-      </c>
-      <c r="L155" t="n">
-        <v/>
-      </c>
-      <c r="M155" t="n">
-        <v/>
-      </c>
-      <c r="N155" t="n">
-        <v/>
-      </c>
-      <c r="O155" t="n">
-        <v/>
-      </c>
-      <c r="P155" t="n">
-        <v/>
-      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>D0=66.47; 最新=2026-06-03; 相对D0=-0.19%</t>
@@ -11215,24 +8878,12 @@
       <c r="J156" s="5" t="n">
         <v>48.33</v>
       </c>
-      <c r="K156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P156" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K156" s="5" t="n"/>
+      <c r="L156" s="5" t="n"/>
+      <c r="M156" s="5" t="n"/>
+      <c r="N156" s="5" t="n"/>
+      <c r="O156" s="5" t="n"/>
+      <c r="P156" s="5" t="n"/>
       <c r="Q156" s="5" t="inlineStr">
         <is>
           <t>D0=48.66; 最新=2026-06-03; 相对D0=-0.68%</t>
@@ -11284,24 +8935,6 @@
       <c r="J157" t="n">
         <v>68.425</v>
       </c>
-      <c r="K157" t="n">
-        <v/>
-      </c>
-      <c r="L157" t="n">
-        <v/>
-      </c>
-      <c r="M157" t="n">
-        <v/>
-      </c>
-      <c r="N157" t="n">
-        <v/>
-      </c>
-      <c r="O157" t="n">
-        <v/>
-      </c>
-      <c r="P157" t="n">
-        <v/>
-      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>D0=72.33; 最新=2026-06-03; 相对D0=-5.40%</t>
@@ -11353,24 +8986,12 @@
       <c r="J158" s="5" t="n">
         <v>140.73</v>
       </c>
-      <c r="K158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P158" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K158" s="5" t="n"/>
+      <c r="L158" s="5" t="n"/>
+      <c r="M158" s="5" t="n"/>
+      <c r="N158" s="5" t="n"/>
+      <c r="O158" s="5" t="n"/>
+      <c r="P158" s="5" t="n"/>
       <c r="Q158" s="5" t="inlineStr">
         <is>
           <t>D0=142.92; 最新=2026-06-03; 相对D0=-1.53%</t>
@@ -11422,24 +9043,12 @@
       <c r="J159" s="5" t="n">
         <v>142.38</v>
       </c>
-      <c r="K159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P159" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K159" s="5" t="n"/>
+      <c r="L159" s="5" t="n"/>
+      <c r="M159" s="5" t="n"/>
+      <c r="N159" s="5" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="5" t="n"/>
       <c r="Q159" s="5" t="inlineStr">
         <is>
           <t>D0=138.58; 最新=2026-06-03; 相对D0=2.74%</t>
@@ -11491,24 +9100,12 @@
       <c r="J160" s="5" t="n">
         <v>419.22</v>
       </c>
-      <c r="K160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P160" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K160" s="5" t="n"/>
+      <c r="L160" s="5" t="n"/>
+      <c r="M160" s="5" t="n"/>
+      <c r="N160" s="5" t="n"/>
+      <c r="O160" s="5" t="n"/>
+      <c r="P160" s="5" t="n"/>
       <c r="Q160" s="5" t="inlineStr">
         <is>
           <t>D0=417.62; 最新=2026-06-03; 相对D0=0.38%</t>
@@ -11560,24 +9157,6 @@
       <c r="J161" t="n">
         <v>199</v>
       </c>
-      <c r="K161" t="n">
-        <v/>
-      </c>
-      <c r="L161" t="n">
-        <v/>
-      </c>
-      <c r="M161" t="n">
-        <v/>
-      </c>
-      <c r="N161" t="n">
-        <v/>
-      </c>
-      <c r="O161" t="n">
-        <v/>
-      </c>
-      <c r="P161" t="n">
-        <v/>
-      </c>
       <c r="Q161" t="inlineStr">
         <is>
           <t>D0=200.40; 最新=2026-06-03; 相对D0=-0.70%</t>
@@ -11629,24 +9208,6 @@
       <c r="J162" t="n">
         <v>12.31</v>
       </c>
-      <c r="K162" t="n">
-        <v/>
-      </c>
-      <c r="L162" t="n">
-        <v/>
-      </c>
-      <c r="M162" t="n">
-        <v/>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>D0=12.72; 最新=2026-06-03; 相对D0=-3.22%</t>
@@ -11698,24 +9259,6 @@
       <c r="J163" t="n">
         <v>11.1206</v>
       </c>
-      <c r="K163" t="n">
-        <v/>
-      </c>
-      <c r="L163" t="n">
-        <v/>
-      </c>
-      <c r="M163" t="n">
-        <v/>
-      </c>
-      <c r="N163" t="n">
-        <v/>
-      </c>
-      <c r="O163" t="n">
-        <v/>
-      </c>
-      <c r="P163" t="n">
-        <v/>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>D0=11.72; 最新=2026-06-03; 相对D0=-5.11%</t>
@@ -11767,24 +9310,6 @@
       <c r="J164" t="n">
         <v>23.515</v>
       </c>
-      <c r="K164" t="n">
-        <v/>
-      </c>
-      <c r="L164" t="n">
-        <v/>
-      </c>
-      <c r="M164" t="n">
-        <v/>
-      </c>
-      <c r="N164" t="n">
-        <v/>
-      </c>
-      <c r="O164" t="n">
-        <v/>
-      </c>
-      <c r="P164" t="n">
-        <v/>
-      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-03; 相对D0=0.92%</t>
@@ -11836,24 +9361,12 @@
       <c r="J165" s="5" t="n">
         <v>131.53</v>
       </c>
-      <c r="K165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O165" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P165" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K165" s="5" t="n"/>
+      <c r="L165" s="5" t="n"/>
+      <c r="M165" s="5" t="n"/>
+      <c r="N165" s="5" t="n"/>
+      <c r="O165" s="5" t="n"/>
+      <c r="P165" s="5" t="n"/>
       <c r="Q165" s="5" t="inlineStr">
         <is>
           <t>D0=138.17; 最新=2026-06-03; 相对D0=-4.81%</t>
@@ -11905,24 +9418,12 @@
       <c r="J166" s="5" t="n">
         <v>133.575</v>
       </c>
-      <c r="K166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P166" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K166" s="5" t="n"/>
+      <c r="L166" s="5" t="n"/>
+      <c r="M166" s="5" t="n"/>
+      <c r="N166" s="5" t="n"/>
+      <c r="O166" s="5" t="n"/>
+      <c r="P166" s="5" t="n"/>
       <c r="Q166" s="5" t="inlineStr">
         <is>
           <t>D0=133.51; 最新=2026-06-03; 相对D0=0.05%</t>
@@ -11974,24 +9475,12 @@
       <c r="J167" s="5" t="n">
         <v>64.92</v>
       </c>
-      <c r="K167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P167" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K167" s="5" t="n"/>
+      <c r="L167" s="5" t="n"/>
+      <c r="M167" s="5" t="n"/>
+      <c r="N167" s="5" t="n"/>
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="5" t="n"/>
       <c r="Q167" s="5" t="inlineStr">
         <is>
           <t>D0=73.47; 最新=2026-06-03; 相对D0=-11.64%</t>
@@ -12043,24 +9532,12 @@
       <c r="J168" s="5" t="n">
         <v>278.93</v>
       </c>
-      <c r="K168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P168" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K168" s="5" t="n"/>
+      <c r="L168" s="5" t="n"/>
+      <c r="M168" s="5" t="n"/>
+      <c r="N168" s="5" t="n"/>
+      <c r="O168" s="5" t="n"/>
+      <c r="P168" s="5" t="n"/>
       <c r="Q168" s="5" t="inlineStr">
         <is>
           <t>D0=278.02; 最新=2026-06-03; 相对D0=0.33%</t>
@@ -12112,24 +9589,6 @@
       <c r="J169" t="n">
         <v>57.24</v>
       </c>
-      <c r="K169" t="n">
-        <v/>
-      </c>
-      <c r="L169" t="n">
-        <v/>
-      </c>
-      <c r="M169" t="n">
-        <v/>
-      </c>
-      <c r="N169" t="n">
-        <v/>
-      </c>
-      <c r="O169" t="n">
-        <v/>
-      </c>
-      <c r="P169" t="n">
-        <v/>
-      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>D0=56.89; 最新=2026-06-03; 相对D0=0.62%</t>
@@ -12181,24 +9640,12 @@
       <c r="J170" s="5" t="n">
         <v>56.685</v>
       </c>
-      <c r="K170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O170" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P170" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K170" s="5" t="n"/>
+      <c r="L170" s="5" t="n"/>
+      <c r="M170" s="5" t="n"/>
+      <c r="N170" s="5" t="n"/>
+      <c r="O170" s="5" t="n"/>
+      <c r="P170" s="5" t="n"/>
       <c r="Q170" s="5" t="inlineStr">
         <is>
           <t>D0=56.56; 最新=2026-06-03; 相对D0=0.22%</t>
@@ -12250,24 +9697,6 @@
       <c r="J171" t="n">
         <v>495.04</v>
       </c>
-      <c r="K171" t="n">
-        <v/>
-      </c>
-      <c r="L171" t="n">
-        <v/>
-      </c>
-      <c r="M171" t="n">
-        <v/>
-      </c>
-      <c r="N171" t="n">
-        <v/>
-      </c>
-      <c r="O171" t="n">
-        <v/>
-      </c>
-      <c r="P171" t="n">
-        <v/>
-      </c>
       <c r="Q171" t="inlineStr">
         <is>
           <t>D0=508.35; 最新=2026-06-03; 相对D0=-2.62%</t>
@@ -12319,24 +9748,6 @@
       <c r="J172" t="n">
         <v>87.7</v>
       </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="n">
-        <v/>
-      </c>
-      <c r="M172" t="n">
-        <v/>
-      </c>
-      <c r="N172" t="n">
-        <v/>
-      </c>
-      <c r="O172" t="n">
-        <v/>
-      </c>
-      <c r="P172" t="n">
-        <v/>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>D0=87.39; 最新=2026-06-03; 相对D0=0.35%</t>
@@ -12388,24 +9799,12 @@
       <c r="J173" s="5" t="n">
         <v>405.2825</v>
       </c>
-      <c r="K173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O173" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P173" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K173" s="5" t="n"/>
+      <c r="L173" s="5" t="n"/>
+      <c r="M173" s="5" t="n"/>
+      <c r="N173" s="5" t="n"/>
+      <c r="O173" s="5" t="n"/>
+      <c r="P173" s="5" t="n"/>
       <c r="Q173" s="5" t="inlineStr">
         <is>
           <t>D0=392.62; 最新=2026-06-03; 相对D0=3.23%</t>
@@ -12457,24 +9856,12 @@
       <c r="J174" s="5" t="n">
         <v>377.725</v>
       </c>
-      <c r="K174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P174" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K174" s="5" t="n"/>
+      <c r="L174" s="5" t="n"/>
+      <c r="M174" s="5" t="n"/>
+      <c r="N174" s="5" t="n"/>
+      <c r="O174" s="5" t="n"/>
+      <c r="P174" s="5" t="n"/>
       <c r="Q174" s="5" t="inlineStr">
         <is>
           <t>D0=385.51; 最新=2026-06-03; 相对D0=-2.02%</t>
@@ -12526,24 +9913,6 @@
       <c r="J175" t="n">
         <v>265.37</v>
       </c>
-      <c r="K175" t="n">
-        <v/>
-      </c>
-      <c r="L175" t="n">
-        <v/>
-      </c>
-      <c r="M175" t="n">
-        <v/>
-      </c>
-      <c r="N175" t="n">
-        <v/>
-      </c>
-      <c r="O175" t="n">
-        <v/>
-      </c>
-      <c r="P175" t="n">
-        <v/>
-      </c>
       <c r="Q175" t="inlineStr">
         <is>
           <t>D0=274.71; 最新=2026-06-03; 相对D0=-3.40%</t>
@@ -12595,24 +9964,12 @@
       <c r="J176" s="5" t="n">
         <v>14.11</v>
       </c>
-      <c r="K176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P176" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K176" s="5" t="n"/>
+      <c r="L176" s="5" t="n"/>
+      <c r="M176" s="5" t="n"/>
+      <c r="N176" s="5" t="n"/>
+      <c r="O176" s="5" t="n"/>
+      <c r="P176" s="5" t="n"/>
       <c r="Q176" s="5" t="inlineStr">
         <is>
           <t>D0=15.44; 最新=2026-06-03; 相对D0=-8.61%</t>
@@ -12664,24 +10021,12 @@
       <c r="J177" s="5" t="n">
         <v>17.93</v>
       </c>
-      <c r="K177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P177" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K177" s="5" t="n"/>
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" s="5" t="n"/>
+      <c r="N177" s="5" t="n"/>
+      <c r="O177" s="5" t="n"/>
+      <c r="P177" s="5" t="n"/>
       <c r="Q177" s="5" t="inlineStr">
         <is>
           <t>D0=19.54; 最新=2026-06-03; 相对D0=-8.24%</t>
@@ -12733,24 +10078,6 @@
       <c r="J178" t="n">
         <v>333.17</v>
       </c>
-      <c r="K178" t="n">
-        <v/>
-      </c>
-      <c r="L178" t="n">
-        <v/>
-      </c>
-      <c r="M178" t="n">
-        <v/>
-      </c>
-      <c r="N178" t="n">
-        <v/>
-      </c>
-      <c r="O178" t="n">
-        <v/>
-      </c>
-      <c r="P178" t="n">
-        <v/>
-      </c>
       <c r="Q178" t="inlineStr">
         <is>
           <t>D0=334.49; 最新=2026-06-03; 相对D0=-0.39%</t>
@@ -12802,24 +10129,12 @@
       <c r="J179" s="5" t="n">
         <v>153.645</v>
       </c>
-      <c r="K179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P179" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K179" s="5" t="n"/>
+      <c r="L179" s="5" t="n"/>
+      <c r="M179" s="5" t="n"/>
+      <c r="N179" s="5" t="n"/>
+      <c r="O179" s="5" t="n"/>
+      <c r="P179" s="5" t="n"/>
       <c r="Q179" s="5" t="inlineStr">
         <is>
           <t>D0=157.97; 最新=2026-06-03; 相对D0=-2.74%</t>
@@ -12871,24 +10186,6 @@
       <c r="J180" t="n">
         <v>51.75</v>
       </c>
-      <c r="K180" t="n">
-        <v/>
-      </c>
-      <c r="L180" t="n">
-        <v/>
-      </c>
-      <c r="M180" t="n">
-        <v/>
-      </c>
-      <c r="N180" t="n">
-        <v/>
-      </c>
-      <c r="O180" t="n">
-        <v/>
-      </c>
-      <c r="P180" t="n">
-        <v/>
-      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>D0=51.52; 最新=2026-06-03; 相对D0=0.45%</t>
@@ -12940,24 +10237,12 @@
       <c r="J181" s="5" t="n">
         <v>59.15</v>
       </c>
-      <c r="K181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P181" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K181" s="5" t="n"/>
+      <c r="L181" s="5" t="n"/>
+      <c r="M181" s="5" t="n"/>
+      <c r="N181" s="5" t="n"/>
+      <c r="O181" s="5" t="n"/>
+      <c r="P181" s="5" t="n"/>
       <c r="Q181" s="5" t="inlineStr">
         <is>
           <t>D0=57.96; 最新=2026-06-03; 相对D0=2.05%</t>
@@ -13008,24 +10293,6 @@
       </c>
       <c r="J182" t="n">
         <v>50.895</v>
-      </c>
-      <c r="K182" t="n">
-        <v/>
-      </c>
-      <c r="L182" t="n">
-        <v/>
-      </c>
-      <c r="M182" t="n">
-        <v/>
-      </c>
-      <c r="N182" t="n">
-        <v/>
-      </c>
-      <c r="O182" t="n">
-        <v/>
-      </c>
-      <c r="P182" t="n">
-        <v/>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -13263,24 +10530,6 @@
       <c r="J194" t="n">
         <v>45.975</v>
       </c>
-      <c r="K194" t="n">
-        <v/>
-      </c>
-      <c r="L194" t="n">
-        <v/>
-      </c>
-      <c r="M194" t="n">
-        <v/>
-      </c>
-      <c r="N194" t="n">
-        <v/>
-      </c>
-      <c r="O194" t="n">
-        <v/>
-      </c>
-      <c r="P194" t="n">
-        <v/>
-      </c>
       <c r="Q194" t="inlineStr">
         <is>
           <t>D0=45.98; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13332,24 +10581,12 @@
       <c r="J195" s="5" t="n">
         <v>208.775</v>
       </c>
-      <c r="K195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P195" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K195" s="5" t="n"/>
+      <c r="L195" s="5" t="n"/>
+      <c r="M195" s="5" t="n"/>
+      <c r="N195" s="5" t="n"/>
+      <c r="O195" s="5" t="n"/>
+      <c r="P195" s="5" t="n"/>
       <c r="Q195" s="5" t="inlineStr">
         <is>
           <t>D0=208.78; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -13401,24 +10638,6 @@
       <c r="J196" t="n">
         <v>111.83</v>
       </c>
-      <c r="K196" t="n">
-        <v/>
-      </c>
-      <c r="L196" t="n">
-        <v/>
-      </c>
-      <c r="M196" t="n">
-        <v/>
-      </c>
-      <c r="N196" t="n">
-        <v/>
-      </c>
-      <c r="O196" t="n">
-        <v/>
-      </c>
-      <c r="P196" t="n">
-        <v/>
-      </c>
       <c r="Q196" t="inlineStr">
         <is>
           <t>D0=111.83; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13470,24 +10689,6 @@
       <c r="J197" t="n">
         <v>8.435</v>
       </c>
-      <c r="K197" t="n">
-        <v/>
-      </c>
-      <c r="L197" t="n">
-        <v/>
-      </c>
-      <c r="M197" t="n">
-        <v/>
-      </c>
-      <c r="N197" t="n">
-        <v/>
-      </c>
-      <c r="O197" t="n">
-        <v/>
-      </c>
-      <c r="P197" t="n">
-        <v/>
-      </c>
       <c r="Q197" t="inlineStr">
         <is>
           <t>D0=8.44; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13539,24 +10740,6 @@
       <c r="J198" t="n">
         <v>83.20999999999999</v>
       </c>
-      <c r="K198" t="n">
-        <v/>
-      </c>
-      <c r="L198" t="n">
-        <v/>
-      </c>
-      <c r="M198" t="n">
-        <v/>
-      </c>
-      <c r="N198" t="n">
-        <v/>
-      </c>
-      <c r="O198" t="n">
-        <v/>
-      </c>
-      <c r="P198" t="n">
-        <v/>
-      </c>
       <c r="Q198" t="inlineStr">
         <is>
           <t>D0=83.21; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13608,24 +10791,6 @@
       <c r="J199" t="n">
         <v>424.7095</v>
       </c>
-      <c r="K199" t="n">
-        <v/>
-      </c>
-      <c r="L199" t="n">
-        <v/>
-      </c>
-      <c r="M199" t="n">
-        <v/>
-      </c>
-      <c r="N199" t="n">
-        <v/>
-      </c>
-      <c r="O199" t="n">
-        <v/>
-      </c>
-      <c r="P199" t="n">
-        <v/>
-      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>D0=424.71; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13677,24 +10842,12 @@
       <c r="J200" s="5" t="n">
         <v>25.86</v>
       </c>
-      <c r="K200" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L200" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M200" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N200" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O200" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P200" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K200" s="5" t="n"/>
+      <c r="L200" s="5" t="n"/>
+      <c r="M200" s="5" t="n"/>
+      <c r="N200" s="5" t="n"/>
+      <c r="O200" s="5" t="n"/>
+      <c r="P200" s="5" t="n"/>
       <c r="Q200" s="5" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13746,24 +10899,12 @@
       <c r="J201" s="5" t="n">
         <v>64.935</v>
       </c>
-      <c r="K201" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L201" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M201" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N201" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O201" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P201" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K201" s="5" t="n"/>
+      <c r="L201" s="5" t="n"/>
+      <c r="M201" s="5" t="n"/>
+      <c r="N201" s="5" t="n"/>
+      <c r="O201" s="5" t="n"/>
+      <c r="P201" s="5" t="n"/>
       <c r="Q201" s="5" t="inlineStr">
         <is>
           <t>D0=64.94; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -13815,24 +10956,6 @@
       <c r="J202" t="n">
         <v>142.685</v>
       </c>
-      <c r="K202" t="n">
-        <v/>
-      </c>
-      <c r="L202" t="n">
-        <v/>
-      </c>
-      <c r="M202" t="n">
-        <v/>
-      </c>
-      <c r="N202" t="n">
-        <v/>
-      </c>
-      <c r="O202" t="n">
-        <v/>
-      </c>
-      <c r="P202" t="n">
-        <v/>
-      </c>
       <c r="Q202" t="inlineStr">
         <is>
           <t>D0=142.69; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13884,24 +11007,6 @@
       <c r="J203" t="n">
         <v>14.75</v>
       </c>
-      <c r="K203" t="n">
-        <v/>
-      </c>
-      <c r="L203" t="n">
-        <v/>
-      </c>
-      <c r="M203" t="n">
-        <v/>
-      </c>
-      <c r="N203" t="n">
-        <v/>
-      </c>
-      <c r="O203" t="n">
-        <v/>
-      </c>
-      <c r="P203" t="n">
-        <v/>
-      </c>
       <c r="Q203" t="inlineStr">
         <is>
           <t>D0=14.75; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -13953,24 +11058,12 @@
       <c r="J204" s="5" t="n">
         <v>12.1114</v>
       </c>
-      <c r="K204" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L204" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M204" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N204" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O204" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P204" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K204" s="5" t="n"/>
+      <c r="L204" s="5" t="n"/>
+      <c r="M204" s="5" t="n"/>
+      <c r="N204" s="5" t="n"/>
+      <c r="O204" s="5" t="n"/>
+      <c r="P204" s="5" t="n"/>
       <c r="Q204" s="5" t="inlineStr">
         <is>
           <t>D0=12.11; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14022,24 +11115,6 @@
       <c r="J205" t="n">
         <v>16.605</v>
       </c>
-      <c r="K205" t="n">
-        <v/>
-      </c>
-      <c r="L205" t="n">
-        <v/>
-      </c>
-      <c r="M205" t="n">
-        <v/>
-      </c>
-      <c r="N205" t="n">
-        <v/>
-      </c>
-      <c r="O205" t="n">
-        <v/>
-      </c>
-      <c r="P205" t="n">
-        <v/>
-      </c>
       <c r="Q205" t="inlineStr">
         <is>
           <t>D0=16.61; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14091,24 +11166,12 @@
       <c r="J206" s="5" t="n">
         <v>153.645</v>
       </c>
-      <c r="K206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P206" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="5" t="n"/>
+      <c r="M206" s="5" t="n"/>
+      <c r="N206" s="5" t="n"/>
+      <c r="O206" s="5" t="n"/>
+      <c r="P206" s="5" t="n"/>
       <c r="Q206" s="5" t="inlineStr">
         <is>
           <t>D0=153.65; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -14160,24 +11223,12 @@
       <c r="J207" s="5" t="n">
         <v>40.89</v>
       </c>
-      <c r="K207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P207" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K207" s="5" t="n"/>
+      <c r="L207" s="5" t="n"/>
+      <c r="M207" s="5" t="n"/>
+      <c r="N207" s="5" t="n"/>
+      <c r="O207" s="5" t="n"/>
+      <c r="P207" s="5" t="n"/>
       <c r="Q207" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-03; 相对D0=-1.40%</t>
@@ -14198,7 +11249,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -14225,24 +11275,6 @@
       <c r="J208" t="n">
         <v>91.08</v>
       </c>
-      <c r="K208" t="n">
-        <v/>
-      </c>
-      <c r="L208" t="n">
-        <v/>
-      </c>
-      <c r="M208" t="n">
-        <v/>
-      </c>
-      <c r="N208" t="n">
-        <v/>
-      </c>
-      <c r="O208" t="n">
-        <v/>
-      </c>
-      <c r="P208" t="n">
-        <v/>
-      </c>
       <c r="Q208" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-03; 相对D0=0.49%</t>
@@ -14294,24 +11326,12 @@
       <c r="J209" s="5" t="n">
         <v>190.99</v>
       </c>
-      <c r="K209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P209" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K209" s="5" t="n"/>
+      <c r="L209" s="5" t="n"/>
+      <c r="M209" s="5" t="n"/>
+      <c r="N209" s="5" t="n"/>
+      <c r="O209" s="5" t="n"/>
+      <c r="P209" s="5" t="n"/>
       <c r="Q209" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-03; 相对D0=3.40%</t>
@@ -14363,24 +11383,12 @@
       <c r="J210" s="5" t="n">
         <v>142.38</v>
       </c>
-      <c r="K210" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M210" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N210" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O210" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P210" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K210" s="5" t="n"/>
+      <c r="L210" s="5" t="n"/>
+      <c r="M210" s="5" t="n"/>
+      <c r="N210" s="5" t="n"/>
+      <c r="O210" s="5" t="n"/>
+      <c r="P210" s="5" t="n"/>
       <c r="Q210" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-03; 相对D0=4.54%</t>
@@ -14432,24 +11440,6 @@
       <c r="J211" t="n">
         <v>371.05</v>
       </c>
-      <c r="K211" t="n">
-        <v/>
-      </c>
-      <c r="L211" t="n">
-        <v/>
-      </c>
-      <c r="M211" t="n">
-        <v/>
-      </c>
-      <c r="N211" t="n">
-        <v/>
-      </c>
-      <c r="O211" t="n">
-        <v/>
-      </c>
-      <c r="P211" t="n">
-        <v/>
-      </c>
       <c r="Q211" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-03; 相对D0=20.73%</t>
@@ -14501,24 +11491,12 @@
       <c r="J212" s="5" t="n">
         <v>60.225</v>
       </c>
-      <c r="K212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P212" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K212" s="5" t="n"/>
+      <c r="L212" s="5" t="n"/>
+      <c r="M212" s="5" t="n"/>
+      <c r="N212" s="5" t="n"/>
+      <c r="O212" s="5" t="n"/>
+      <c r="P212" s="5" t="n"/>
       <c r="Q212" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-03; 相对D0=4.81%</t>
@@ -14570,24 +11548,12 @@
       <c r="J213" s="5" t="n">
         <v>14.45</v>
       </c>
-      <c r="K213" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L213" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M213" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N213" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O213" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P213" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K213" s="5" t="n"/>
+      <c r="L213" s="5" t="n"/>
+      <c r="M213" s="5" t="n"/>
+      <c r="N213" s="5" t="n"/>
+      <c r="O213" s="5" t="n"/>
+      <c r="P213" s="5" t="n"/>
       <c r="Q213" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-03; 相对D0=8.24%</t>
@@ -14639,24 +11605,12 @@
       <c r="J214" s="5" t="n">
         <v>59.155</v>
       </c>
-      <c r="K214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P214" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K214" s="5" t="n"/>
+      <c r="L214" s="5" t="n"/>
+      <c r="M214" s="5" t="n"/>
+      <c r="N214" s="5" t="n"/>
+      <c r="O214" s="5" t="n"/>
+      <c r="P214" s="5" t="n"/>
       <c r="Q214" s="5" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-03; 相对D0=2.26%</t>
@@ -14708,24 +11662,12 @@
       <c r="J215" s="5" t="n">
         <v>56.7</v>
       </c>
-      <c r="K215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P215" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K215" s="5" t="n"/>
+      <c r="L215" s="5" t="n"/>
+      <c r="M215" s="5" t="n"/>
+      <c r="N215" s="5" t="n"/>
+      <c r="O215" s="5" t="n"/>
+      <c r="P215" s="5" t="n"/>
       <c r="Q215" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-03; 相对D0=0.35%</t>
@@ -14777,24 +11719,6 @@
       <c r="J216" t="n">
         <v>133.785</v>
       </c>
-      <c r="K216" t="n">
-        <v/>
-      </c>
-      <c r="L216" t="n">
-        <v/>
-      </c>
-      <c r="M216" t="n">
-        <v/>
-      </c>
-      <c r="N216" t="n">
-        <v/>
-      </c>
-      <c r="O216" t="n">
-        <v/>
-      </c>
-      <c r="P216" t="n">
-        <v/>
-      </c>
       <c r="Q216" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-03; 相对D0=5.83%</t>
@@ -14846,24 +11770,12 @@
       <c r="J217" s="5" t="n">
         <v>106.6</v>
       </c>
-      <c r="K217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P217" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K217" s="5" t="n"/>
+      <c r="L217" s="5" t="n"/>
+      <c r="M217" s="5" t="n"/>
+      <c r="N217" s="5" t="n"/>
+      <c r="O217" s="5" t="n"/>
+      <c r="P217" s="5" t="n"/>
       <c r="Q217" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-03; 相对D0=-7.87%</t>
@@ -14915,24 +11827,12 @@
       <c r="J218" s="5" t="n">
         <v>266.11</v>
       </c>
-      <c r="K218" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L218" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M218" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N218" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O218" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P218" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K218" s="5" t="n"/>
+      <c r="L218" s="5" t="n"/>
+      <c r="M218" s="5" t="n"/>
+      <c r="N218" s="5" t="n"/>
+      <c r="O218" s="5" t="n"/>
+      <c r="P218" s="5" t="n"/>
       <c r="Q218" s="5" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-03; 相对D0=-7.06%</t>
@@ -14984,24 +11884,12 @@
       <c r="J219" s="5" t="n">
         <v>199.07</v>
       </c>
-      <c r="K219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P219" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K219" s="5" t="n"/>
+      <c r="L219" s="5" t="n"/>
+      <c r="M219" s="5" t="n"/>
+      <c r="N219" s="5" t="n"/>
+      <c r="O219" s="5" t="n"/>
+      <c r="P219" s="5" t="n"/>
       <c r="Q219" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-03; 相对D0=8.80%</t>
@@ -15053,24 +11941,6 @@
       <c r="J220" t="n">
         <v>495.04</v>
       </c>
-      <c r="K220" t="n">
-        <v/>
-      </c>
-      <c r="L220" t="n">
-        <v/>
-      </c>
-      <c r="M220" t="n">
-        <v/>
-      </c>
-      <c r="N220" t="n">
-        <v/>
-      </c>
-      <c r="O220" t="n">
-        <v/>
-      </c>
-      <c r="P220" t="n">
-        <v/>
-      </c>
       <c r="Q220" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-03; 相对D0=3.00%</t>
@@ -15122,24 +11992,12 @@
       <c r="J221" s="5" t="n">
         <v>116.63</v>
       </c>
-      <c r="K221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P221" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K221" s="5" t="n"/>
+      <c r="L221" s="5" t="n"/>
+      <c r="M221" s="5" t="n"/>
+      <c r="N221" s="5" t="n"/>
+      <c r="O221" s="5" t="n"/>
+      <c r="P221" s="5" t="n"/>
       <c r="Q221" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-03; 相对D0=26.32%</t>
@@ -15191,24 +12049,12 @@
       <c r="J222" s="5" t="n">
         <v>76.06</v>
       </c>
-      <c r="K222" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M222" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N222" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O222" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P222" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K222" s="5" t="n"/>
+      <c r="L222" s="5" t="n"/>
+      <c r="M222" s="5" t="n"/>
+      <c r="N222" s="5" t="n"/>
+      <c r="O222" s="5" t="n"/>
+      <c r="P222" s="5" t="n"/>
       <c r="Q222" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-03; 相对D0=9.34%</t>
@@ -15260,24 +12106,6 @@
       <c r="J223" t="n">
         <v>286.8299</v>
       </c>
-      <c r="K223" t="n">
-        <v/>
-      </c>
-      <c r="L223" t="n">
-        <v/>
-      </c>
-      <c r="M223" t="n">
-        <v/>
-      </c>
-      <c r="N223" t="n">
-        <v/>
-      </c>
-      <c r="O223" t="n">
-        <v/>
-      </c>
-      <c r="P223" t="n">
-        <v/>
-      </c>
       <c r="Q223" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-03; 相对D0=0.64%</t>
@@ -15329,24 +12157,12 @@
       <c r="J224" s="5" t="n">
         <v>182.59</v>
       </c>
-      <c r="K224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P224" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K224" s="5" t="n"/>
+      <c r="L224" s="5" t="n"/>
+      <c r="M224" s="5" t="n"/>
+      <c r="N224" s="5" t="n"/>
+      <c r="O224" s="5" t="n"/>
+      <c r="P224" s="5" t="n"/>
       <c r="Q224" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-03; 相对D0=6.37%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -15398,24 +12214,12 @@
       <c r="J225" s="5" t="n">
         <v>416.25</v>
       </c>
-      <c r="K225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P225" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K225" s="5" t="n"/>
+      <c r="L225" s="5" t="n"/>
+      <c r="M225" s="5" t="n"/>
+      <c r="N225" s="5" t="n"/>
+      <c r="O225" s="5" t="n"/>
+      <c r="P225" s="5" t="n"/>
       <c r="Q225" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-03; 相对D0=15.15%</t>
@@ -15467,24 +12271,6 @@
       <c r="J226" t="n">
         <v>25.2299</v>
       </c>
-      <c r="K226" t="n">
-        <v/>
-      </c>
-      <c r="L226" t="n">
-        <v/>
-      </c>
-      <c r="M226" t="n">
-        <v/>
-      </c>
-      <c r="N226" t="n">
-        <v/>
-      </c>
-      <c r="O226" t="n">
-        <v/>
-      </c>
-      <c r="P226" t="n">
-        <v/>
-      </c>
       <c r="Q226" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-03; 相对D0=33.63%</t>
@@ -15536,24 +12322,6 @@
       <c r="J227" t="n">
         <v>112.1</v>
       </c>
-      <c r="K227" t="n">
-        <v/>
-      </c>
-      <c r="L227" t="n">
-        <v/>
-      </c>
-      <c r="M227" t="n">
-        <v/>
-      </c>
-      <c r="N227" t="n">
-        <v/>
-      </c>
-      <c r="O227" t="n">
-        <v/>
-      </c>
-      <c r="P227" t="n">
-        <v/>
-      </c>
       <c r="Q227" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-03; 相对D0=-2.25%</t>
@@ -15605,24 +12373,12 @@
       <c r="J228" s="5" t="n">
         <v>133.575</v>
       </c>
-      <c r="K228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P228" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K228" s="5" t="n"/>
+      <c r="L228" s="5" t="n"/>
+      <c r="M228" s="5" t="n"/>
+      <c r="N228" s="5" t="n"/>
+      <c r="O228" s="5" t="n"/>
+      <c r="P228" s="5" t="n"/>
       <c r="Q228" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-03; 相对D0=-0.38%</t>
@@ -15674,24 +12430,12 @@
       <c r="J229" s="5" t="n">
         <v>265.37</v>
       </c>
-      <c r="K229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P229" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K229" s="5" t="n"/>
+      <c r="L229" s="5" t="n"/>
+      <c r="M229" s="5" t="n"/>
+      <c r="N229" s="5" t="n"/>
+      <c r="O229" s="5" t="n"/>
+      <c r="P229" s="5" t="n"/>
       <c r="Q229" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-03; 相对D0=3.97%</t>
@@ -15743,24 +12487,6 @@
       <c r="J230" t="n">
         <v>107.125</v>
       </c>
-      <c r="K230" t="n">
-        <v/>
-      </c>
-      <c r="L230" t="n">
-        <v/>
-      </c>
-      <c r="M230" t="n">
-        <v/>
-      </c>
-      <c r="N230" t="n">
-        <v/>
-      </c>
-      <c r="O230" t="n">
-        <v/>
-      </c>
-      <c r="P230" t="n">
-        <v/>
-      </c>
       <c r="Q230" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-03; 相对D0=1.40%</t>
@@ -15812,24 +12538,12 @@
       <c r="J231" s="5" t="n">
         <v>182.59</v>
       </c>
-      <c r="K231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P231" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" s="5" t="n"/>
+      <c r="N231" s="5" t="n"/>
+      <c r="O231" s="5" t="n"/>
+      <c r="P231" s="5" t="n"/>
       <c r="Q231" s="5" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-03; 相对D0=11.96%</t>
@@ -15881,24 +12595,6 @@
       <c r="J232" t="n">
         <v>66.345</v>
       </c>
-      <c r="K232" t="n">
-        <v/>
-      </c>
-      <c r="L232" t="n">
-        <v/>
-      </c>
-      <c r="M232" t="n">
-        <v/>
-      </c>
-      <c r="N232" t="n">
-        <v/>
-      </c>
-      <c r="O232" t="n">
-        <v/>
-      </c>
-      <c r="P232" t="n">
-        <v/>
-      </c>
       <c r="Q232" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-03; 相对D0=2.69%</t>
@@ -15950,24 +12646,12 @@
       <c r="J233" s="5" t="n">
         <v>140.73</v>
       </c>
-      <c r="K233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P233" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K233" s="5" t="n"/>
+      <c r="L233" s="5" t="n"/>
+      <c r="M233" s="5" t="n"/>
+      <c r="N233" s="5" t="n"/>
+      <c r="O233" s="5" t="n"/>
+      <c r="P233" s="5" t="n"/>
       <c r="Q233" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-03; 相对D0=3.68%</t>
@@ -16019,24 +12703,6 @@
       <c r="J234" t="n">
         <v>618.09</v>
       </c>
-      <c r="K234" t="n">
-        <v/>
-      </c>
-      <c r="L234" t="n">
-        <v/>
-      </c>
-      <c r="M234" t="n">
-        <v/>
-      </c>
-      <c r="N234" t="n">
-        <v/>
-      </c>
-      <c r="O234" t="n">
-        <v/>
-      </c>
-      <c r="P234" t="n">
-        <v/>
-      </c>
       <c r="Q234" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-03; 相对D0=2.93%</t>
@@ -16088,24 +12754,12 @@
       <c r="J235" s="5" t="n">
         <v>32.05</v>
       </c>
-      <c r="K235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P235" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K235" s="5" t="n"/>
+      <c r="L235" s="5" t="n"/>
+      <c r="M235" s="5" t="n"/>
+      <c r="N235" s="5" t="n"/>
+      <c r="O235" s="5" t="n"/>
+      <c r="P235" s="5" t="n"/>
       <c r="Q235" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-03; 相对D0=28.92%</t>
@@ -16156,24 +12810,6 @@
       </c>
       <c r="J236" t="n">
         <v>421.34</v>
-      </c>
-      <c r="K236" t="n">
-        <v/>
-      </c>
-      <c r="L236" t="n">
-        <v/>
-      </c>
-      <c r="M236" t="n">
-        <v/>
-      </c>
-      <c r="N236" t="n">
-        <v/>
-      </c>
-      <c r="O236" t="n">
-        <v/>
-      </c>
-      <c r="P236" t="n">
-        <v/>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -16271,7 +12907,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16283,7 +12918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16554,7 +13189,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -16839,7 +13474,6 @@
       <c r="M11" s="19" t="n">
         <v>0.021638</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -17024,7 +13658,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -17043,7 +13676,6 @@
       <c r="M15" s="19" t="n">
         <v>0.09188200000000001</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -17296,9 +13928,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="14" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17344,9 +13974,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="14" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17392,9 +14020,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="14" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -17440,9 +14066,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="14" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17492,9 +14116,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="14" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -17540,9 +14162,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="14" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -17588,9 +14208,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="14" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -17636,9 +14254,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="14" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17684,9 +14300,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="14" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -17816,7 +14430,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17828,7 +14441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18508,7 +15121,6 @@
       <c r="O12" s="22" t="n">
         <v>-0.019095</v>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18537,7 +15149,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -18624,7 +15235,6 @@
       <c r="O14" s="22" t="n">
         <v>-0.00011</v>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18653,7 +15263,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -18711,7 +15320,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -18736,7 +15344,6 @@
       <c r="O16" s="19" t="n">
         <v>0.024966</v>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -19377,9 +15984,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="14" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19431,9 +16036,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="14" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -19485,9 +16088,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="14" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19539,9 +16140,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="14" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -19651,9 +16250,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19665,7 +16261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -19936,7 +16532,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -19996,7 +16592,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -20190,7 +16786,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -20221,7 +16816,6 @@
       <c r="Q9" s="19" t="n">
         <v>0.19779</v>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20250,7 +16844,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -20413,7 +17006,6 @@
       <c r="Q12" s="19" t="n">
         <v>0.045112</v>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -20810,9 +17402,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="14" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -20870,9 +17460,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="14" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -20975,10 +17563,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20990,7 +17574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21425,7 +18009,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -21567,7 +18151,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -22739,7 +19322,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -22786,7 +19369,6 @@
       <c r="S26" s="19" t="n">
         <v>0.039567</v>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -22809,7 +19391,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -22941,7 +19523,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -23271,9 +19853,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="14" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -23337,9 +19917,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="14" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23403,9 +19981,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="14" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23469,9 +20045,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="14" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -23535,9 +20109,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="14" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23601,9 +20173,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="14" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -23667,9 +20237,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="14" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23804,8 +20372,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23817,7 +20383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -23978,24 +20544,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24047,24 +20601,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24116,24 +20658,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24185,24 +20715,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24254,24 +20772,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24323,24 +20823,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24392,24 +20880,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24461,24 +20937,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24530,24 +20988,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24599,24 +21045,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24668,24 +21102,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24737,24 +21159,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24806,24 +21216,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24875,24 +21267,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24944,24 +21318,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25013,24 +21369,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25082,24 +21426,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25151,24 +21483,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25220,24 +21534,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25474,24 +21776,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25536,11 +21826,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25552,7 +21837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25725,7 +22010,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -26181,7 +22465,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -26633,7 +22916,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -26785,7 +23067,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -27161,7 +23442,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -27237,7 +23517,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -27313,7 +23592,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -27383,7 +23661,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -27465,7 +23743,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -27508,7 +23785,6 @@
       <c r="U26" s="22" t="n">
         <v>-0.011056</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -27531,7 +23807,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -27835,7 +24111,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -27911,7 +24187,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -28325,9 +24601,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="14" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28429,11 +24703,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28651,7 +24920,6 @@
       <c r="V2" t="n">
         <v>205.7700042724609</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.89; 4H分金=50.11</t>
@@ -28739,7 +25007,6 @@
       <c r="V3" t="n">
         <v>275.4400024414062</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.60; 4H分金=48.02</t>
@@ -28821,8 +25088,6 @@
       <c r="T4" t="b">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
         <v>84</v>
       </c>
@@ -28913,7 +25178,6 @@
       <c r="V5" t="n">
         <v>50.72499847412109</v>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=50.72; Gann0=35.68; 段涨幅=42.17%</t>
@@ -29001,7 +25265,6 @@
       <c r="V6" t="n">
         <v>50.72499847412109</v>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.73; 4H分金=38.73</t>
@@ -29089,7 +25352,6 @@
       <c r="V7" t="n">
         <v>122.3000030517578</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=53.33; 4H分金=50.79</t>
@@ -29171,8 +25433,6 @@
       <c r="T8" t="b">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="n">
         <v>87</v>
       </c>
@@ -29353,7 +25613,6 @@
       <c r="V10" t="n">
         <v>16.90999984741211</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.16; 4H分金=47.45</t>
@@ -29441,7 +25700,6 @@
       <c r="V11" t="n">
         <v>245.9499969482422</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=245.95; Gann0=148.95; 段涨幅=65.13%</t>
@@ -29529,7 +25787,6 @@
       <c r="V12" t="n">
         <v>211.3399963378906</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.15; 4H分金=47.61</t>
@@ -29617,7 +25874,6 @@
       <c r="V13" t="n">
         <v>132.1499938964844</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=132.15; Gann0=94.82; 段涨幅=39.37%</t>
@@ -29705,7 +25961,6 @@
       <c r="V14" t="n">
         <v>132.1499938964844</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.18; 4H分金=44.12</t>
@@ -29793,7 +26048,6 @@
       <c r="V15" t="n">
         <v>278.7049865722656</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.82; 4H分金=47.93</t>
@@ -29875,8 +26129,6 @@
       <c r="T16" t="b">
         <v>0</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
         <v>93</v>
       </c>
@@ -29967,7 +26219,6 @@
       <c r="V17" t="n">
         <v>9.689999580383301</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=9.69; Gann0=6.73; 段涨幅=43.98%</t>
@@ -30055,7 +26306,6 @@
       <c r="V18" t="n">
         <v>9.689999580383301</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.67; 4H分金=40.42</t>
@@ -30233,7 +26483,6 @@
       <c r="V20" t="n">
         <v>94.40000152587891</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=94.40; Gann0=73.18; 段涨幅=29.00%</t>
@@ -30321,7 +26570,6 @@
       <c r="V21" t="n">
         <v>94.40000152587891</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.80; 4H分金=39.76</t>
@@ -30409,7 +26657,6 @@
       <c r="V22" t="n">
         <v>108.0599975585938</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.33; 4H分金=46.01</t>
@@ -30677,7 +26924,6 @@
       <c r="V25" t="n">
         <v>204.8000030517578</v>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.09; 4H分金=40.55</t>
@@ -31395,7 +27641,6 @@
       <c r="V33" t="n">
         <v>466.3200073242188</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=466.32; Gann0=409.58; 段涨幅=13.85%</t>
@@ -31483,7 +27728,6 @@
       <c r="V34" t="n">
         <v>466.3200073242188</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.53; 4H分金=35.62</t>
@@ -31571,7 +27815,6 @@
       <c r="V35" t="n">
         <v>31.59000015258789</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=31.59; Gann0=21.72; 段涨幅=45.46%</t>
@@ -31659,7 +27902,6 @@
       <c r="V36" t="n">
         <v>31.59000015258789</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.27; 4H分金=31.01</t>
@@ -31747,7 +27989,6 @@
       <c r="V37" t="n">
         <v>139.1999969482422</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.21; 4H分金=48.31</t>
@@ -31829,8 +28070,6 @@
       <c r="T38" t="b">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
         <v>98</v>
       </c>
@@ -31921,7 +28160,6 @@
       <c r="V39" t="n">
         <v>232.2799987792969</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.13; 4H分金=40.81</t>
@@ -32099,7 +28337,6 @@
       <c r="V41" t="n">
         <v>163.1300048828125</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.56; 4H分金=50.39</t>
@@ -32187,7 +28424,6 @@
       <c r="V42" t="n">
         <v>73.86000061035156</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=73.86; Gann0=53.96; 段涨幅=36.89%</t>
@@ -32275,7 +28511,6 @@
       <c r="V43" t="n">
         <v>302.9500122070312</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=62.61; 4H分金=50.80</t>
@@ -32363,7 +28598,6 @@
       <c r="V44" t="n">
         <v>163.6999969482422</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=163.70; Gann0=131.63; 段涨幅=24.36%</t>
@@ -32451,7 +28685,6 @@
       <c r="V45" t="n">
         <v>163.6999969482422</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.54; 4H分金=36.58</t>
@@ -32539,7 +28772,6 @@
       <c r="V46" t="n">
         <v>112.2099990844727</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.94; 4H分金=48.89</t>
@@ -32627,7 +28859,6 @@
       <c r="V47" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=16.76; Gann0=12.71; 段涨幅=31.86%</t>
@@ -32715,7 +28946,6 @@
       <c r="V48" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=14.30; Gann0=9.66; 段涨幅=47.96%</t>
@@ -32803,7 +29033,6 @@
       <c r="V49" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.54; 4H分金=39.88</t>
@@ -33071,7 +29300,6 @@
       <c r="V52" t="n">
         <v>18.79500007629395</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=18.80; Gann0=14.92; 段涨幅=25.97%</t>
@@ -33159,7 +29387,6 @@
       <c r="V53" t="n">
         <v>18.79500007629395</v>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.77; 4H分金=34.97</t>
@@ -33247,7 +29474,6 @@
       <c r="V54" t="n">
         <v>75.59999847412109</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.90; 4H分金=43.83</t>
@@ -33335,7 +29561,6 @@
       <c r="V55" t="n">
         <v>119.379997253418</v>
       </c>
-      <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.37; 4H分金=47.38</t>
@@ -33603,7 +29828,6 @@
       <c r="V58" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=167.40; Gann0=132.66; 段涨幅=26.19%</t>
@@ -33685,8 +29909,6 @@
       <c r="T59" t="b">
         <v>0</v>
       </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
       <c r="W59" t="n">
         <v>90</v>
       </c>
@@ -33848,7 +30070,6 @@
       <c r="D2" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" s="8" t="n">
         <v>46175</v>
       </c>
@@ -33954,7 +30175,6 @@
       <c r="D4" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34114,7 +30334,6 @@
       <c r="D7" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34166,7 +30385,6 @@
       <c r="D8" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="8" t="n">
         <v>46168</v>
       </c>
@@ -34218,7 +30436,6 @@
       <c r="D9" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34270,7 +30487,6 @@
       <c r="D10" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="8" t="n">
         <v>46175</v>
       </c>
@@ -34376,7 +30592,6 @@
       <c r="D12" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34428,7 +30643,6 @@
       <c r="D13" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="8" t="n">
         <v>46168</v>
       </c>
@@ -34534,7 +30748,6 @@
       <c r="D15" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34586,7 +30799,6 @@
       <c r="D16" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="8" t="n">
         <v>46175</v>
       </c>
@@ -34635,7 +30847,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34744,7 +30955,6 @@
       <c r="D19" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34904,7 +31114,6 @@
       <c r="D22" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" s="8" t="n">
         <v>46164</v>
       </c>
@@ -35737,7 +31946,6 @@
       <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" s="8" t="n">
         <v>46175</v>
       </c>
@@ -36419,7 +32627,6 @@
       <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" s="8" t="n">
         <v>46171</v>
       </c>
@@ -36531,7 +32738,6 @@
       <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" s="8" t="n">
         <v>46169</v>
       </c>
@@ -36563,7 +32769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -37317,9 +33523,7 @@
           <t>APLD</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="14" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -37347,9 +33551,7 @@
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B30" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="14" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -37377,9 +33579,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B31" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="14" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -37407,9 +33607,7 @@
           <t>EOSE</t>
         </is>
       </c>
-      <c r="B32" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="14" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -37437,9 +33635,7 @@
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="14" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -37467,9 +33663,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="15" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -37488,8 +33682,6 @@
       <c r="F34" t="n">
         <v>424.7095</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -37497,9 +33689,7 @@
           <t>NNE</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="14" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -37527,9 +33717,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="14" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -37557,9 +33745,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -37578,8 +33764,6 @@
       <c r="F37" t="n">
         <v>142.685</v>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -37587,9 +33771,7 @@
           <t>RUN</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -37608,8 +33790,6 @@
       <c r="F38" t="n">
         <v>14.75</v>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -37617,9 +33797,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="14" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -37647,9 +33825,7 @@
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="14" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -37677,9 +33853,7 @@
           <t>VST</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -37698,8 +33872,6 @@
       <c r="F41" t="n">
         <v>153.645</v>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
@@ -37791,7 +33963,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38035,7 +34206,6 @@
       <c r="I6" s="19" t="n">
         <v>0.009227000000000001</v>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -38138,7 +34308,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -38178,7 +34348,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
@@ -38218,7 +34388,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -39043,7 +35213,6 @@
       <c r="I32" s="19" t="n">
         <v>0.004464</v>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -39159,7 +35328,6 @@
       <c r="I35" s="19" t="n">
         <v>0.006152</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -39199,7 +35367,6 @@
       <c r="I36" s="19" t="n">
         <v>0.003547</v>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -39304,14 +35471,12 @@
       <c r="F39" t="n">
         <v>315.2</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>310.09</v>
       </c>
       <c r="I39" s="22" t="n">
         <v>-0.016212</v>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -39340,14 +35505,12 @@
       <c r="F40" t="n">
         <v>72.33</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>68.425</v>
       </c>
       <c r="I40" s="22" t="n">
         <v>-0.053989</v>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -39376,14 +35539,12 @@
       <c r="F41" t="n">
         <v>11.72</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>11.1206</v>
       </c>
       <c r="I41" s="22" t="n">
         <v>-0.051143</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
@@ -39613,7 +35774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -39720,7 +35881,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -39944,7 +36105,6 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.5</v>
       </c>
@@ -40078,7 +36238,6 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.68</v>
       </c>
@@ -40091,7 +36250,6 @@
       <c r="K11" s="19" t="n">
         <v>0.001361</v>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -40212,7 +36370,6 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.25</v>
       </c>
@@ -40225,7 +36382,6 @@
       <c r="K14" s="22" t="n">
         <v>-0.053594</v>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -40363,7 +36519,6 @@
       <c r="K17" s="19" t="n">
         <v>0.030242</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -40920,9 +37075,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="14" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -40962,9 +37115,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="14" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -41008,9 +37159,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="14" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -41050,9 +37199,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="14" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -41092,9 +37239,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="14" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -41134,9 +37279,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="14" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -41176,9 +37319,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="14" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="14" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -41302,7 +37443,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
